--- a/180V DC Driver/180VDCDriver_Satın_Alım.xlsx
+++ b/180V DC Driver/180VDCDriver_Satın_Alım.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enes-\Desktop\180V DC Driver\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enes-\Desktop\MEM_R\180V DC Driver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C398C9-EB01-4C03-AD3F-B0F09437BFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5440B9-4822-447C-B1CE-0C99047B276A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,32 +36,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Rectifier</t>
   </si>
   <si>
-    <t>https://www.robotistan.com/kbpc5010-1000v-50a-masa-tipi-kopru-diyot</t>
-  </si>
-  <si>
     <t>Capacitor Bulk</t>
   </si>
   <si>
     <t>Capacitor Film</t>
   </si>
   <si>
-    <t>https://www.entegredunyasi.com.tr/urun/5uf300v-kutu-tipi-mkp-rm-27-5mm?srsltid=AfmBOorbdkLgThHe0bS7dnSE7U0AOE7qQr4zJL8AQ2IogfQSX0Th1mA-VVY</t>
-  </si>
-  <si>
     <t>TLP250 optocoupler</t>
   </si>
   <si>
-    <t>https://www.direnc.net/tlp250-soic8-smd-mosfet-cikis-optokuplor-entegresi?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=0100-pmax-alfa&amp;gad_source=1&amp;gad_campaignid=22157331511&amp;gbraid=0AAAAAD2u3wpdm4OIGs1AiULmPj94VqJoQ&amp;gclid=Cj0KCQjwm6POBhCrARIsAIG58CLK9MluHz7OE2REnIv6Kly9IsNsvojPXOqQhFevDzkmoIthpx-hViUaAkdrEALw_wcB</t>
-  </si>
-  <si>
-    <t>https://www.direnc.net/pcb-tip-sigorta-yuvasi-20mm-siyah--kapak-haric</t>
-  </si>
-  <si>
     <t>Sigorta tutacağı</t>
   </si>
   <si>
@@ -74,23 +62,53 @@
     <t>MOSFET</t>
   </si>
   <si>
-    <t>https://www.direnc.net/irfp460--20a-500v-027ohm-n-channel-si-power-mosfet-to-247</t>
-  </si>
-  <si>
     <t>https://www.motorobit.com/1000uf-400v-elektrolitik-kondansator-35x60mm?srsltid=AfmBOoqetNQ5iZG3gGWjhmJEcvIEY6K23yJGOCSIIAmTkfIhtfUocIMx4Po</t>
   </si>
   <si>
-    <t>https://www.robotistan.com/kf301v-5</t>
-  </si>
-  <si>
-    <t>Güç konnektör</t>
+    <t>Power Connector</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/4-7uf-630v-dc-mkp-polyester-kondansator</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/kbpc5010w-1000v-50a-pcb-type-kopru-diyot</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/tlp250-f-dip-8-transistor-output-optocoupler</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/6x30-kablolu-sigorta-yuvasi-siyah</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/irfp460pbf-to-247-500v-20a-mosfet</t>
+  </si>
+  <si>
+    <t>Termistör</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/ntc-10d-2-power-ntc-termistor-ntc10d-20</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/xp126-5mm-2-pin-terminal-klemens-yesil</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/5-ila-5a-acs712-akim-sensoru</t>
+  </si>
+  <si>
+    <t>Akım Sensörü</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/4a-6x30mm-gecikmeli-seramik-sigorta</t>
+  </si>
+  <si>
+    <t>Sigorta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +123,29 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,10 +169,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -427,97 +471,97 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2">
-        <v>88.63</v>
+        <v>11</v>
+      </c>
+      <c r="C1" s="3">
+        <v>88.3</v>
       </c>
       <c r="D1">
         <v>1</v>
       </c>
       <c r="E1">
         <f>C1*D1</f>
-        <v>88.63</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>243</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E8" si="0">C2*D2</f>
-        <v>243</v>
+        <f t="shared" ref="E2:E11" si="0">C2*D2</f>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>53.32</v>
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>107.03</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
         <f t="shared" si="0"/>
-        <v>53.32</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2">
-        <v>68.81</v>
+        <v>12</v>
+      </c>
+      <c r="C4" s="3">
+        <v>64.22</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>68.81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5.29</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4">
+        <v>17.5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>5.29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>24.3</v>
@@ -532,55 +576,100 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2">
-        <v>63.51</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>141.81</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>63.51</v>
+        <v>141.81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="2">
-        <v>3.78</v>
+        <v>6.55</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>11.34</v>
+        <v>19.649999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="2"/>
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3">
+        <v>32.11</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
       <c r="E9">
-        <f>SUM(E1:E8)</f>
-        <v>558.20000000000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="2"/>
+        <f t="shared" si="0"/>
+        <v>32.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="34.5" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5">
+        <v>95.55</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>95.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34.5" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5">
+        <v>9.83</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>49.15</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
+      <c r="E12">
+        <f>SUM(E1:E11)</f>
+        <v>1143.1199999999999</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
@@ -601,9 +690,15 @@
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" xr:uid="{AF4C46A3-4E17-4E4B-A772-57710F9AB035}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{7A7EA5BA-8741-4FD4-99E5-455CAE360265}"/>
-    <hyperlink ref="B4" r:id="rId3" display="https://www.direnc.net/tlp250-soic8-smd-mosfet-cikis-optokuplor-entegresi?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=0100-pmax-alfa&amp;gad_source=1&amp;gad_campaignid=22157331511&amp;gbraid=0AAAAAD2u3wpdm4OIGs1AiULmPj94VqJoQ&amp;gclid=Cj0KCQjwm6POBhCrARIsAIG58CLK9MluHz7OE2REnIv6Kly9IsNsvojPXOqQhFevDzkmoIthpx-hViUaAkdrEALw_wcB" xr:uid="{B2355786-A781-4A76-BFB3-C958DA3462B4}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{7A13A89D-E13E-41F9-81AD-7DEF2AB3E4DE}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{7A13A89D-E13E-41F9-81AD-7DEF2AB3E4DE}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{39BD885C-5ED3-4E5A-A586-8D2DEBF05ED8}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{9CCE00C7-B24A-4120-97D9-5AB3B477F6ED}"/>
+    <hyperlink ref="B9" r:id="rId6" xr:uid="{FE9A88B6-CCAF-42DE-86CB-2DFD0E8F0998}"/>
+    <hyperlink ref="B10" r:id="rId7" xr:uid="{0B44A90C-CC9A-4722-9F26-AF4BF0DD9A80}"/>
+    <hyperlink ref="B8" r:id="rId8" xr:uid="{2B072CEF-4E60-4D76-B588-205C17D8D12E}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{A0EC3F28-3D59-4E9A-90DA-5AB3316B6641}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/180V DC Driver/180VDCDriver_Satın_Alım.xlsx
+++ b/180V DC Driver/180VDCDriver_Satın_Alım.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enes-\Desktop\MEM_R\180V DC Driver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5440B9-4822-447C-B1CE-0C99047B276A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9FF8DB-7455-4077-B3F8-7FF5011B8837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Rectifier</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Power Connector</t>
   </si>
   <si>
-    <t>https://www.ulutaselektronik.com/urun/4-7uf-630v-dc-mkp-polyester-kondansator</t>
-  </si>
-  <si>
     <t>https://www.ulutaselektronik.com/urun/kbpc5010w-1000v-50a-pcb-type-kopru-diyot</t>
   </si>
   <si>
@@ -102,13 +99,55 @@
   </si>
   <si>
     <t>Sigorta</t>
+  </si>
+  <si>
+    <t>Varistör</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/350vac-560vdc-10mm-varistor-10d561k</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/kf-03-pcb-tip-kapakli-sigorta-yuvasi-5x20-sigort</t>
+  </si>
+  <si>
+    <t>Sigorta yuvası 12V için</t>
+  </si>
+  <si>
+    <t>10Uf elektrolitik</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/220nf-50v-seramik-kondansator-10-adet</t>
+  </si>
+  <si>
+    <t>220nf 50V *10</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/hlk-pm12-12v-3w-pcb-tipi-trafo-transformator</t>
+  </si>
+  <si>
+    <t>12V 3W PCB Tipi Voltaj Dönüştürücü</t>
+  </si>
+  <si>
+    <t>500mA sigorta</t>
+  </si>
+  <si>
+    <t>https://www.motorobit.com/500ma-5x20mm-gecikmeli-cam-sigorta</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/10uf-400v-105c-10x17-elektrolitik-aluminyum-kondansator</t>
+  </si>
+  <si>
+    <t>https://www.ulutaselektronik.com/urun/1uf-450vac-rm-28mm-polyester-kondansator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₺&quot;#,##0.00;[Red]\-&quot;₺&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +186,21 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3D84B5"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0C122A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -169,13 +223,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -457,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -471,17 +528,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="3">
-        <v>88.3</v>
+        <v>76.44</v>
       </c>
       <c r="D1">
         <v>1</v>
       </c>
       <c r="E1">
         <f>C1*D1</f>
-        <v>88.3</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -492,14 +549,14 @@
         <v>8</v>
       </c>
       <c r="C2" s="2">
-        <v>243</v>
+        <v>253.8</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E11" si="0">C2*D2</f>
-        <v>486</v>
+        <f t="shared" ref="E2:E17" si="0">C2*D2</f>
+        <v>507.6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -507,17 +564,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>107.03</v>
+        <v>33</v>
+      </c>
+      <c r="C3" s="8">
+        <v>20.85</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <f t="shared" si="0"/>
-        <v>107.03</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -525,17 +582,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>64.22</v>
+        <v>66.709999999999994</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>64.22</v>
+        <v>66.709999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
@@ -543,17 +600,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4">
-        <v>17.5</v>
+        <v>9.02</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -564,14 +621,14 @@
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>24.3</v>
+        <v>25.38</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>24.3</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -579,17 +636,17 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>141.81</v>
+        <v>183.46</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>141.81</v>
+        <v>183.46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -597,25 +654,25 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
-        <v>6.55</v>
+        <v>6.77</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>19.649999999999999</v>
+        <v>20.309999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>32.11</v>
@@ -630,61 +687,153 @@
     </row>
     <row r="10" spans="1:5" ht="34.5" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5">
-        <v>95.55</v>
+        <v>98.7</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>95.55</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34.5" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5">
-        <v>9.83</v>
+        <v>10.15</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>49.15</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2.82</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
       <c r="E12">
-        <f>SUM(E1:E11)</f>
-        <v>1143.1199999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
+        <f t="shared" si="0"/>
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.35</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>2.35</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="2"/>
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2">
+        <v>7.41</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>14.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="6">
+        <v>15.23</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>15.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="6">
+        <v>219.96</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>219.96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6">
+        <v>3.38</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <f>SUM(E1:E17)</f>
+        <v>1411.8999999999999</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -697,8 +846,16 @@
     <hyperlink ref="B10" r:id="rId7" xr:uid="{0B44A90C-CC9A-4722-9F26-AF4BF0DD9A80}"/>
     <hyperlink ref="B8" r:id="rId8" xr:uid="{2B072CEF-4E60-4D76-B588-205C17D8D12E}"/>
     <hyperlink ref="B11" r:id="rId9" xr:uid="{A0EC3F28-3D59-4E9A-90DA-5AB3316B6641}"/>
+    <hyperlink ref="B15" r:id="rId10" xr:uid="{9973D147-76E6-451C-AE92-2DA9B4313C7C}"/>
+    <hyperlink ref="B17" r:id="rId11" xr:uid="{327DE21A-8F4D-4F57-B363-F62972914F79}"/>
+    <hyperlink ref="B4" r:id="rId12" xr:uid="{E534FE1D-EE1E-47BA-9EAD-51ED6B96F5FC}"/>
+    <hyperlink ref="B7" r:id="rId13" xr:uid="{5BDB2F13-72A1-4656-B7EC-03744587918C}"/>
+    <hyperlink ref="B12" r:id="rId14" xr:uid="{D64FA521-4B59-49F8-88FC-4BE28F0D2188}"/>
+    <hyperlink ref="B13" r:id="rId15" xr:uid="{FA954162-A31A-487E-895C-AF463DBAAFA6}"/>
+    <hyperlink ref="B14" r:id="rId16" xr:uid="{77B05FAE-861B-48BB-A1DA-0B3F2CA7790C}"/>
+    <hyperlink ref="B16" r:id="rId17" xr:uid="{C339418A-A0CA-45F7-9BAA-A4E505D45F55}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>